--- a/PLAN_EMPRESA_CAIXABANK/anexo-financiero.xlsx
+++ b/PLAN_EMPRESA_CAIXABANK/anexo-financiero.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,6 +99,12 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -128,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -150,11 +156,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,6 +291,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -356,12 +417,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Histórico'!$B$4:$D$4</f>
+              <f>'Histórico'!$B$4:$E$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Histórico'!$B$5:$D$5</f>
+              <f>'Histórico'!$B$5:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -912,7 +973,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Los datos históricos (hoja «Histórico») proceden del P&amp;L de gestión de la actividad Ekio y están PENDIENTES de contraste con el Holded actualizado y las declaraciones fiscales (IRPF, modelos 130 y 390) antes de su presentación formal.</t>
+          <t>Los datos históricos (hoja «Histórico») abarcan los ejercicios 2023–2026 (H1) de la actividad Ekio. El ejercicio 2023 recoge únicamente la facturación (junio–diciembre, año de arranque); su margen y resultado quedan PENDIENTES. Todo el histórico está pendiente de contraste con el Holded actualizado y las declaraciones fiscales (IRPF, modelos 130 y 390) antes de su presentación formal.</t>
         </is>
       </c>
     </row>
@@ -963,13 +1024,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -994,15 +1056,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>2026 (H1)</t>
         </is>
@@ -1015,12 +1082,15 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
+        <v>390000</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <v>534504</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="D5" s="12" t="n">
         <v>537845</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="E5" s="12" t="n">
         <v>207815</v>
       </c>
     </row>
@@ -1030,13 +1100,18 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>n.d. [PENDIENTE]</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>0.384</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="D6" s="13" t="n">
         <v>0.245</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="E6" s="13" t="n">
         <v>0.5590000000000001</v>
       </c>
     </row>
@@ -1046,9 +1121,10 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
-      <c r="B7" s="14">
-        <f>B5*B6</f>
-        <v/>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>n.d. [PENDIENTE]</t>
+        </is>
       </c>
       <c r="C7" s="14">
         <f>C5*C6</f>
@@ -1058,6 +1134,10 @@
         <f>D5*D6</f>
         <v/>
       </c>
+      <c r="E7" s="14">
+        <f>E5*E6</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -1065,9 +1145,10 @@
           <t>Coste de ventas implícito (€)</t>
         </is>
       </c>
-      <c r="B8" s="14">
-        <f>B5-B7</f>
-        <v/>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>n.d. [PENDIENTE]</t>
+        </is>
       </c>
       <c r="C8" s="14">
         <f>C5-C7</f>
@@ -1077,6 +1158,10 @@
         <f>D5-D7</f>
         <v/>
       </c>
+      <c r="E8" s="14">
+        <f>E5-E7</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -1084,14 +1169,33 @@
           <t>Resultado del ejercicio (€)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>n.d. [PENDIENTE]</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>52493</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="D9" s="12" t="n">
         <v>19301</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>78738</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Facturación acumulada 2023 – junio 2026 (cifra ACUMULADA del periodo, no anual)</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="n"/>
+      <c r="C10" s="40" t="n"/>
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="42">
+        <f>SUM(B5:E5)</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -1102,16 +1206,25 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>PENDIENTE (Javier): facturación 2023, cierre provisional jul/ago 2026 e informe de Holded actualizado para adjuntar como anexo.</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2023 corresponde a ~7 meses de actividad (junio–diciembre), año de arranque del negocio. Margen y resultado pendientes de las declaraciones fiscales del ejercicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>PENDIENTE (Javier): cierre provisional jul/ago 2026 e informe de Holded actualizado para adjuntar como anexo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A11:D11"/>
+  <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
